--- a/03-Customer Form Configuration/customer-form-configuration-testcases-EN.xlsx
+++ b/03-Customer Form Configuration/customer-form-configuration-testcases-EN.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3557,15 +3557,6 @@
           <t>Profile Photo toggle shows ON</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3640,15 +3631,6 @@
           <t>Display Name, Title, First Name, Middle Name, Last Name, Citizen ID, Date of Birth, Blood Type, Gender — all toggles ON</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3723,15 +3705,6 @@
           <t>Toast success · page reloads with toggle state matching what was set</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3807,15 +3780,6 @@
           <t>Profile Photo field ✅ · Personal Details 9 fields ✅ · Preferences fields ✅ (per toggle state)</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3890,15 +3854,6 @@
           <t>Toggle shows OFF</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3973,15 +3928,6 @@
           <t>Toast success · config persisted</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4057,15 +4003,6 @@
           <t>Date of Birth NOT shown in Personal Details on the Add Customer page</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4140,15 +4077,6 @@
           <t>Toggle shows ON</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4223,15 +4151,6 @@
           <t>Toast success · config persisted</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4307,15 +4226,6 @@
           <t>Blood Type appears in Personal Details on the Add Customer page</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4390,15 +4300,6 @@
           <t>3 toggles show OFF</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4473,15 +4374,6 @@
           <t>Toast success · all 3 field changes persisted</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4557,15 +4449,6 @@
           <t>Profile Photo ❌ · Date of Birth ❌ · Note ❌ (none of the 3 appear)</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4640,15 +4523,6 @@
           <t>Personal Details section body is hidden (collapsed)</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4723,15 +4597,454 @@
           <t>Personal Details section body expands, showing all 9 fields</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AICC</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CC Super App</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Customer Form Configuration</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DFC_TA02</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Toggle all Personal Details fields OFF → Save → none appear on Add Customer</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>All-OFF edge case — PO confirmed (HA-DFC1): any field can be toggled OFF, no exceptions</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>- Login User: ketwadee
+- Role &amp; Permission: All Permission - Contact Configuration
+- On the Customer Form Configuration page</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DFC_TA02_TC-01</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Set all 9 Personal Details fields = OFF</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>SYSTEMTEST</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Toggle OFF: Display Name · Title · First Name · Middle Name · Last Name · Citizen ID · Date of Birth · Blood Type · Gender</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>All 9 Personal Details toggles show OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AICC</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CC Super App</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Customer Form Configuration</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DFC_TA02</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Toggle all Personal Details fields OFF → Save → none appear on Add Customer</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>All-OFF edge case — PO confirmed (HA-DFC1): any field can be toggled OFF, no exceptions</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>- Login User: ketwadee
+- Role &amp; Permission: All Permission - Contact Configuration
+- On the Customer Form Configuration page</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>DFC_TA02_TC-02</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Save Configuration</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>SYSTEMTEST</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Click 'Save Configuration' button</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Toast success · all 9 field changes persisted</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AICC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CC Super App</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Customer Form Configuration</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DFC_TA02</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Toggle all Personal Details fields OFF → Save → none appear on Add Customer</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>All-OFF edge case — PO confirmed (HA-DFC1): any field can be toggled OFF, no exceptions</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>- Login User: ketwadee
+- Role &amp; Permission: All Permission - Contact Configuration
+- Save Configuration completed
+- On the Add Customer page</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>DFC_TA02_TC-03</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Verify no Personal Details fields appear on Add Customer</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>SYSTEMTEST</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Go to Add Customer → view Personal Details section</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>None of the 9 Personal Details fields appear (Display Name ❌ Title ❌ First Name ❌ ... — all hidden, no exception)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AICC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CC Super App</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Customer Form Configuration</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DFC_TA03</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Toggle field OFF (existing data) → hidden not cleared → toggle ON restores data</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Data-safety — PO confirmed (HA-DFC2): toggle OFF does not clear customer data, hidden only</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>- Login User: ketwadee
+- Role &amp; Permission: All Permission - Contact Configuration
+- Existing customer record with Date of Birth data
+- On the Customer Form Configuration page</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>DFC_TA03_TC-01</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Toggle Date of Birth = OFF → Save Configuration</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>SYSTEMTEST</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Toggle Date of Birth → OFF · Click Save Configuration</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Toast success · Date of Birth toggle = OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AICC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CC Super App</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Customer Form Configuration</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DFC_TA03</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Toggle field OFF (existing data) → hidden not cleared → toggle ON restores data</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Data-safety — PO confirmed (HA-DFC2): toggle OFF does not clear customer data, hidden only</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>- Login User: ketwadee
+- Role &amp; Permission: All Permission - Contact Configuration
+- Save Configuration completed
+- On the Edit Customer page (customer with existing DOB)</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>DFC_TA03_TC-02</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Verify Date of Birth hidden on Edit Customer (data not shown, not cleared)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>SYSTEMTEST</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Go to Edit Customer (customer with existing DOB) → view Personal Details section</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Date of Birth field NOT visible on Edit Customer form (hidden) · customer record still exists in system</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AICC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CC Super App</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Customer Form Configuration</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DFC_TA03</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Toggle field OFF (existing data) → hidden not cleared → toggle ON restores data</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Data-safety — PO confirmed (HA-DFC2): toggle OFF does not clear customer data, hidden only</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>- Login User: ketwadee
+- Role &amp; Permission: All Permission - Contact Configuration
+- Existing customer record with Date of Birth data
+- On the Customer Form Configuration page</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>DFC_TA03_TC-03</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Toggle Date of Birth = ON → Save → Verify original data returns</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>SYSTEMTEST</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Toggle Date of Birth → ON · Click Save Configuration · Go to Edit Customer again</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Date of Birth field visible again on Edit Customer · original date value intact (not cleared)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
